--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T10:23:38+00:00</t>
+    <t>2025-02-24T13:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:55:23+00:00</t>
+    <t>2025-02-26T08:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T08:56:44+00:00</t>
+    <t>2025-03-04T11:06:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T11:06:18+00:00</t>
+    <t>2025-03-06T12:24:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T12:24:43+00:00</t>
+    <t>2025-03-20T12:28:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T12:28:15+00:00</t>
+    <t>2025-03-24T06:28:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-condition</t>
+    <t>https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-condition</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T06:28:05+00:00</t>
+    <t>2025-03-24T07:27:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -656,7 +656,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/ValueSet/at-aps-problems</t>
+    <t>https://fhir.hl7.at/elga/aps/r4/ValueSet/at-aps-problems</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -720,7 +720,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-patient)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient)
 </t>
   </si>
   <si>
@@ -1409,7 +1409,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="89.3984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="69.87109375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1424,7 +1424,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="85.23828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.41015625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="53.15625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T07:27:46+00:00</t>
+    <t>2025-03-24T07:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T10:23:29+00:00</t>
+    <t>2026-01-28T10:05:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -851,7 +851,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -978,7 +978,7 @@
     <t>Condition.stage.assessment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ClinicalImpression|4.0.1|DiagnosticReport|4.0.1|Observation|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-clinicalimpression|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-diagnosticreport|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observation)
 </t>
   </si>
   <si>
@@ -1420,7 +1420,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="68.421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="182.5078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T10:05:57+00:00</t>
+    <t>2026-01-29T06:33:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T06:33:09+00:00</t>
+    <t>2026-02-03T10:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:06:44+00:00</t>
+    <t>2026-02-03T10:34:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:34:36+00:00</t>
+    <t>2026-02-09T07:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T07:50:08+00:00</t>
+    <t>2026-02-13T12:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T12:44:21+00:00</t>
+    <t>2026-02-16T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T08:31:54+00:00</t>
+    <t>2026-02-16T11:13:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T11:13:42+00:00</t>
+    <t>2026-02-17T09:00:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T09:00:43+00:00</t>
+    <t>2026-09-01T07:40:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
